--- a/naver-place-crawler/results_derma/남구_피부과.xlsx
+++ b/naver-place-crawler/results_derma/남구_피부과.xlsx
@@ -624,10 +624,10 @@
         <v>3632</v>
       </c>
       <c r="Q2" t="n">
-        <v>9994</v>
+        <v>9995</v>
       </c>
       <c r="R2" t="n">
-        <v>13626</v>
+        <v>13627</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -685,12 +685,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -706,12 +706,12 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -906,10 +906,10 @@
         <v>1434</v>
       </c>
       <c r="Q5" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="R5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -943,11 +943,7 @@
           <t>마리의원</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>marines8385@naver.com</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
@@ -1094,10 +1090,10 @@
         <v>272</v>
       </c>
       <c r="Q7" t="n">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="R7" t="n">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1155,7 +1151,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1319,7 +1315,11 @@
           <t>문피부과의원</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>de_calcomani@naver.com</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
@@ -1414,11 +1414,7 @@
           <t>re-ele@naver.com</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>webtick@gmail.com</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>1644-2638</t>
@@ -1437,7 +1433,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1470,10 +1466,10 @@
         <v>2230</v>
       </c>
       <c r="Q11" t="n">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="R11" t="n">
-        <v>2989</v>
+        <v>2991</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1561,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q12" t="n">
         <v>74</v>
       </c>
       <c r="R12" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1695,11 +1691,7 @@
           <t>세란피부과의원</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>lllllhope@naver.com</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -1903,7 +1895,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1973,11 +1965,7 @@
           <t>리앤리의원</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>inme2022@naver.com</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
@@ -2255,7 +2243,11 @@
           <t>리버스의원 인천구월 터미널역</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>wlskfl9087@naver.com</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
@@ -2280,7 +2272,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2308,10 +2300,10 @@
         <v>632</v>
       </c>
       <c r="Q20" t="n">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="R20" t="n">
-        <v>2810</v>
+        <v>2809</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2496,10 +2488,10 @@
         <v>1858</v>
       </c>
       <c r="Q22" t="n">
-        <v>6814</v>
+        <v>6818</v>
       </c>
       <c r="R22" t="n">
-        <v>8672</v>
+        <v>8676</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2815,11 +2807,7 @@
           <t>인천CNP차앤박피부과</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>cnpskin07@naver.com</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
@@ -2844,7 +2832,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3191,11 +3179,7 @@
           <t>장피부과의원</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1sanginfl@naver.com</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>jangskin@lycos.co.kr</t>
@@ -3289,7 +3273,11 @@
           <t>이지피부과</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>towhsb@naver.com</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
@@ -3501,12 +3489,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3595,7 +3583,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3722,10 +3710,10 @@
         <v>248</v>
       </c>
       <c r="Q35" t="n">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="R35" t="n">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3855,7 +3843,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>limka0917@naver.com</t>
+          <t>social_forum@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -4102,10 +4090,10 @@
         <v>9367</v>
       </c>
       <c r="Q39" t="n">
-        <v>2378</v>
+        <v>2393</v>
       </c>
       <c r="R39" t="n">
-        <v>11745</v>
+        <v>11760</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4327,11 +4315,7 @@
           <t>맑고고운의원 옥련송도역점</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>value_trend_guide@naver.com</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
@@ -4666,10 +4650,10 @@
         <v>43</v>
       </c>
       <c r="Q45" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="R45" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -5504,10 +5488,10 @@
         <v>5244</v>
       </c>
       <c r="Q54" t="n">
-        <v>3927</v>
+        <v>3935</v>
       </c>
       <c r="R54" t="n">
-        <v>9171</v>
+        <v>9179</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5565,12 +5549,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5659,7 +5643,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5692,10 +5676,10 @@
         <v>1516</v>
       </c>
       <c r="Q56" t="n">
-        <v>5069</v>
+        <v>5070</v>
       </c>
       <c r="R56" t="n">
-        <v>6585</v>
+        <v>6586</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -6105,7 +6089,11 @@
           <t>주안연세의원</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>lan_j_97@naver.com</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
@@ -6289,11 +6277,7 @@
           <t>봄헤어뷰티살롱</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>yallycry@naver.com</t>
-        </is>
-      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
@@ -6665,11 +6649,7 @@
           <t>한상희비뇨기과의원</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>yurim2224@naver.com</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
@@ -6759,7 +6739,11 @@
           <t>인하비뇨기과의원</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>binterest@naver.com</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
@@ -6784,7 +6768,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6849,11 +6833,7 @@
           <t>이인의비뇨기과의원</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>binterest@naver.com</t>
-        </is>
-      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
@@ -6943,11 +6923,7 @@
           <t>W여성병원</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>jeilwomen@naver.com</t>
-        </is>
-      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
@@ -7000,10 +6976,10 @@
         <v>6165</v>
       </c>
       <c r="Q70" t="n">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="R70" t="n">
-        <v>8331</v>
+        <v>8332</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7070,7 +7046,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7135,7 +7111,11 @@
           <t>쑥쑥튼튼소아청소년과의원</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>tteumodo@naver.com</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
@@ -7470,10 +7450,10 @@
         <v>1126</v>
       </c>
       <c r="Q75" t="n">
-        <v>5322</v>
+        <v>5324</v>
       </c>
       <c r="R75" t="n">
-        <v>6448</v>
+        <v>6450</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_derma/남구_피부과.xlsx
+++ b/naver-place-crawler/results_derma/남구_피부과.xlsx
@@ -624,10 +624,10 @@
         <v>3632</v>
       </c>
       <c r="Q2" t="n">
-        <v>9995</v>
+        <v>10002</v>
       </c>
       <c r="R2" t="n">
-        <v>13627</v>
+        <v>13634</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -685,12 +685,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -706,22 +706,22 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>3017</v>
       </c>
       <c r="Q3" t="n">
-        <v>5504</v>
+        <v>5508</v>
       </c>
       <c r="R3" t="n">
-        <v>8521</v>
+        <v>8525</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -943,7 +943,11 @@
           <t>마리의원</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>marines8385@naver.com</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
@@ -1090,10 +1094,10 @@
         <v>272</v>
       </c>
       <c r="Q7" t="n">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="R7" t="n">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1151,7 +1155,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1221,11 +1225,7 @@
           <t>이룸의원</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>erumclinic@naver.com</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
@@ -1414,7 +1414,11 @@
           <t>re-ele@naver.com</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>webtick@gmail.com</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>1644-2638</t>
@@ -1433,7 +1437,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1466,10 +1470,10 @@
         <v>2230</v>
       </c>
       <c r="Q11" t="n">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="R11" t="n">
-        <v>2991</v>
+        <v>2993</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1691,7 +1695,11 @@
           <t>세란피부과의원</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>lllllhope@naver.com</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -1831,13 +1839,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3149</v>
+        <v>3151</v>
       </c>
       <c r="Q15" t="n">
         <v>7154</v>
       </c>
       <c r="R15" t="n">
-        <v>10303</v>
+        <v>10305</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1895,7 +1903,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1965,7 +1973,11 @@
           <t>리앤리의원</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>inme2022@naver.com</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
@@ -2055,11 +2067,7 @@
           <t>세이미휴먼피부과의원</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>asczc32121a@naver.com</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
@@ -2272,7 +2280,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2488,10 +2496,10 @@
         <v>1858</v>
       </c>
       <c r="Q22" t="n">
-        <v>6818</v>
+        <v>6817</v>
       </c>
       <c r="R22" t="n">
-        <v>8676</v>
+        <v>8675</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2807,7 +2815,11 @@
           <t>인천CNP차앤박피부과</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>cnpskin07@naver.com</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
@@ -2832,7 +2844,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3179,7 +3191,11 @@
           <t>장피부과의원</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1sanginfl@naver.com</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>jangskin@lycos.co.kr</t>
@@ -3428,10 +3444,10 @@
         <v>1428</v>
       </c>
       <c r="Q32" t="n">
-        <v>4820</v>
+        <v>4821</v>
       </c>
       <c r="R32" t="n">
-        <v>6248</v>
+        <v>6249</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3489,12 +3505,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3583,7 +3599,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4087,13 +4103,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>9367</v>
+        <v>9370</v>
       </c>
       <c r="Q39" t="n">
-        <v>2393</v>
+        <v>2396</v>
       </c>
       <c r="R39" t="n">
-        <v>11760</v>
+        <v>11766</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4315,7 +4331,11 @@
           <t>맑고고운의원 옥련송도역점</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>value_trend_guide@naver.com</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
@@ -4556,10 +4576,10 @@
         <v>1336</v>
       </c>
       <c r="Q44" t="n">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="R44" t="n">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4687,7 +4707,11 @@
           <t>서울피부과의원 홈플러스간석점</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>120voice@naver.com</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
@@ -4777,7 +4801,11 @@
           <t>삼성수의원</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>lindsay0626@naver.com</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
@@ -5149,7 +5177,11 @@
           <t>에이치봄의원</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>sky001iii@naver.com</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>COPYRIGHT2020@HBOM.COM</t>
@@ -5488,10 +5520,10 @@
         <v>5244</v>
       </c>
       <c r="Q54" t="n">
-        <v>3935</v>
+        <v>3946</v>
       </c>
       <c r="R54" t="n">
-        <v>9179</v>
+        <v>9190</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5549,12 +5581,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5643,7 +5675,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5955,13 +5987,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1908</v>
+        <v>1911</v>
       </c>
       <c r="Q59" t="n">
         <v>31</v>
       </c>
       <c r="R59" t="n">
-        <v>1939</v>
+        <v>1942</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6277,7 +6309,11 @@
           <t>봄헤어뷰티살롱</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>yallycry@naver.com</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
@@ -6649,7 +6685,11 @@
           <t>한상희비뇨기과의원</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>yurim2224@naver.com</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
@@ -6739,11 +6779,7 @@
           <t>인하비뇨기과의원</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>binterest@naver.com</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
@@ -6768,7 +6804,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6833,7 +6869,11 @@
           <t>이인의비뇨기과의원</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>binterest@naver.com</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
@@ -6923,7 +6963,11 @@
           <t>W여성병원</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>jeilwomen@naver.com</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
@@ -6976,10 +7020,10 @@
         <v>6165</v>
       </c>
       <c r="Q70" t="n">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="R70" t="n">
-        <v>8332</v>
+        <v>8333</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7046,7 +7090,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7111,11 +7155,7 @@
           <t>쑥쑥튼튼소아청소년과의원</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>tteumodo@naver.com</t>
-        </is>
-      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
@@ -7450,10 +7490,10 @@
         <v>1126</v>
       </c>
       <c r="Q75" t="n">
-        <v>5324</v>
+        <v>5327</v>
       </c>
       <c r="R75" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7484,33 +7524,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>더원한방병원 인천</t>
+          <t>경희백한방병원</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>myeongjiju846@naver.com</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>cid@spo.go.kr</t>
-        </is>
-      </c>
+          <t>khbaekhospital@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>032-433-7575</t>
+          <t>032-887-1079</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 402 초정빌딩 2, 3, 4층 더원한방병원</t>
+          <t>인천광역시 미추홀구 아암대로 91</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>http://www.theonemedi.com</t>
+          <t>https://khbmc.com/</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7536,7 +7572,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7545,13 +7581,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="Q76" t="n">
-        <v>3286</v>
+        <v>5652</v>
       </c>
       <c r="R76" t="n">
-        <v>3533</v>
+        <v>5918</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7560,12 +7596,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1490412672</t>
+          <t>13241397</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1490412672</t>
+          <t>https://m.place.naver.com/place/13241397</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">

--- a/naver-place-crawler/results_derma/남구_피부과.xlsx
+++ b/naver-place-crawler/results_derma/남구_피부과.xlsx
@@ -423,7 +423,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VS라인의원 인천구월점</t>
+          <t>뷰티크의원 인천구월</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>vsline_official@naver.com</t>
+          <t>txnfgw@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1436-7591</t>
+          <t>0507-1395-3851</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로507번길 9 하나빌딩 4층</t>
+          <t>인천광역시 남동구 예술로 126 5층 504호, 505호, 506호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://ingw.vsline.kr</t>
+          <t>https://beautyqueclinic3.com/?utm_source=naver&amp;utm_medium=referral&amp;utm_campaign=PL_GW</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3632</v>
+        <v>1912</v>
       </c>
       <c r="Q2" t="n">
-        <v>10002</v>
+        <v>6723</v>
       </c>
       <c r="R2" t="n">
-        <v>13634</v>
+        <v>8635</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>31059087</t>
+          <t>1308418932</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31059087</t>
+          <t>https://m.place.naver.com/place/1308418932</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -658,39 +658,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>블리비의원 인천구월점</t>
+          <t>에이치봄의원</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ksjk-2@naver.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>youn_0u0@naver.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>COPYRIGHT2020@HBOM.COM</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1670-9056</t>
+          <t>0507-1348-8201</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로489번길 4 맨하탄빌딩 12층</t>
+          <t>인천광역시 미추홀구 독배로 309 노블레스타워 503, 504호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://www.velyb.kr/</t>
+          <t>http://www.hbom.kr</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -706,22 +710,22 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3017</v>
+        <v>471</v>
       </c>
       <c r="Q3" t="n">
-        <v>5508</v>
+        <v>166</v>
       </c>
       <c r="R3" t="n">
-        <v>8525</v>
+        <v>637</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1056691133</t>
+          <t>1722351848</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1056691133</t>
+          <t>https://m.place.naver.com/place/1722351848</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -752,34 +756,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>썸블리의원</t>
+          <t>이룸의원</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pparksomin@naver.com</t>
+          <t>erumclinic@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1488-1110</t>
+          <t>032-577-2624</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로507번길 18 4층</t>
+          <t>인천광역시 서구 원적로 102-2 가좌한신휴플러스상가 201호, 301호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://some3vely.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -800,22 +804,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1015</v>
+        <v>387</v>
       </c>
       <c r="Q4" t="n">
-        <v>2154</v>
+        <v>44</v>
       </c>
       <c r="R4" t="n">
-        <v>3169</v>
+        <v>431</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1446767766</t>
+          <t>41496712</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446767766</t>
+          <t>https://m.place.naver.com/place/41496712</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -846,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>메인의원 인천주안점</t>
+          <t>삼성수의원</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dudnf8970@naver.com</t>
+          <t>lindsay0626@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1334-8970</t>
+          <t>0507-1493-8277</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 716 204호, 205호, 206호</t>
+          <t>인천광역시 미추홀구 소성로 135 6층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dudnf8970</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,12 +882,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,17 +903,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1434</v>
+        <v>194</v>
       </c>
       <c r="Q5" t="n">
-        <v>569</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>2003</v>
+        <v>195</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13106424</t>
+          <t>19513486</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13106424</t>
+          <t>https://m.place.naver.com/place/19513486</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -940,34 +944,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>마리의원</t>
+          <t>닥터쁘띠의원 인천구월</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>marines8385@naver.com</t>
+          <t>nervous7314@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>032-429-3330</t>
+          <t>0507-1333-3008</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로507번길 9 하나프라자 201호</t>
+          <t>인천광역시 남동구 예술로 126 링크126빌딩 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.mariclinic.co.kr/</t>
+          <t>https://guwol.doctorpetit.com/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -988,22 +992,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>46</v>
+        <v>1732</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>3748</v>
       </c>
       <c r="R6" t="n">
-        <v>53</v>
+        <v>5480</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>12859533</t>
+          <t>1657854067</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12859533</t>
+          <t>https://m.place.naver.com/place/1657854067</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>리브의원 인천</t>
+          <t>닥터디자이너의원 인천점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>reev_incheon@naver.com</t>
+          <t>drdclinic_ic@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>032-724-8544</t>
+          <t>032-1544-0247</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 예술로140번길 35 5층</t>
+          <t>인천광역시 남동구 인하로507번길 22 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://incheon.reevclinic.com/</t>
+          <t>https://icn.drdclinic.co.kr</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,7 +1070,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1076,10 +1080,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wk6hkei</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>O</t>
@@ -1087,17 +1095,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>272</v>
+        <v>1221</v>
       </c>
       <c r="Q7" t="n">
-        <v>1353</v>
+        <v>250</v>
       </c>
       <c r="R7" t="n">
-        <v>1625</v>
+        <v>1471</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1114,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1113664560</t>
+          <t>1854673021</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1113664560</t>
+          <t>https://m.place.naver.com/place/1854673021</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1136,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>인천 맘모스헤어라인의원</t>
+          <t>아비쥬의원 인천구월</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dawoonam@naver.com</t>
+          <t>abijou0@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1346-5855</t>
+          <t>1544-0377</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 예술로140번길 35 위너스글로벌타워 3층</t>
+          <t>인천광역시 남동구 인하로507번길 4 한성빌딩 9, 10층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.mammothincheon.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1160,20 +1168,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4lq4a</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>O</t>
@@ -1185,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2551</v>
       </c>
       <c r="Q8" t="n">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="R8" t="n">
-        <v>49</v>
+        <v>2664</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1212,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1388271254</t>
+          <t>21235475</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1388271254</t>
+          <t>https://m.place.naver.com/place/21235475</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1222,25 +1234,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>이룸의원</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>나인문의원</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ninemoonclinic@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>032-577-2624</t>
+          <t>1644-8349</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 102-2 가좌한신휴플러스상가 201호, 301호</t>
+          <t>인천광역시 남동구 인하로 501 슈페리어빌딩 6층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://ninemoonclinic.co.kr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1250,7 +1266,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1271,17 +1287,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>381</v>
+        <v>1345</v>
       </c>
       <c r="Q9" t="n">
-        <v>44</v>
+        <v>1024</v>
       </c>
       <c r="R9" t="n">
-        <v>425</v>
+        <v>2369</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1306,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>41496712</t>
+          <t>1279049941</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/41496712</t>
+          <t>https://m.place.naver.com/place/1279049941</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1312,24 +1328,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>문피부과의원</t>
+          <t>리앤리의원</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>de_calcomani@naver.com</t>
+          <t>inme2022@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>032-867-0365</t>
+          <t>032-420-0205</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인하로 275</t>
+          <t>인천광역시 미추홀구 경원대로 869 르네상스빌딩</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1369,13 +1385,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>764</v>
+        <v>229</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>770</v>
+        <v>230</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,17 +1400,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>34414120</t>
+          <t>13551782</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34414120</t>
+          <t>https://m.place.naver.com/place/13551782</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1406,38 +1422,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>리엘르의원 인천점</t>
+          <t>인천CNP차앤박피부과</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>re-ele@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>webtick@gmail.com</t>
-        </is>
-      </c>
+          <t>thwjd0018@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1644-2638</t>
+          <t>032-455-1155</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로507번길 63 6층 601호</t>
+          <t>인천광역시 남동구 예술로 138 이토타워 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://ic.re-ele.com/</t>
+          <t>https://www.cnpskin.com/pc/branch/main/main.html?jijummid=cnpskin13</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1463,17 +1475,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2230</v>
+        <v>1652</v>
       </c>
       <c r="Q11" t="n">
-        <v>763</v>
+        <v>14</v>
       </c>
       <c r="R11" t="n">
-        <v>2993</v>
+        <v>1666</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1494,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1990116476</t>
+          <t>11705835</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1990116476</t>
+          <t>https://m.place.naver.com/place/11705835</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1504,34 +1516,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>하프의원 인천</t>
+          <t>더마티스트의원 인천</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>chjh0421@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>dermartist_clinic@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>u003c4leaf.ysh@gmail.com</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>032-428-7212</t>
+          <t>0507-1301-7985</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로 497-5 4층 401호</t>
+          <t>인천광역시 남동구 예술로 126 7층 701호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://halfclinic2.com/</t>
+          <t>https://www.Dermartist.com/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1541,7 +1557,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1561,13 +1577,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>67</v>
+        <v>1442</v>
       </c>
       <c r="Q12" t="n">
-        <v>74</v>
+        <v>4681</v>
       </c>
       <c r="R12" t="n">
-        <v>141</v>
+        <v>6123</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1592,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2009568151</t>
+          <t>1541439004</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009568151</t>
+          <t>https://m.place.naver.com/place/1541439004</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1598,39 +1614,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>닥터디자이너의원 인천점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>drdclinic_ic@naver.com</t>
-        </is>
-      </c>
+          <t>마리의원</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>032-1544-0247</t>
+          <t>032-429-3330</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로507번길 22 3층</t>
+          <t>인천광역시 남동구 인하로507번길 9 하나프라자 201호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://icn.drdclinic.co.kr</t>
+          <t>http://www.mariclinic.co.kr/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1646,22 +1658,22 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1221</v>
+        <v>46</v>
       </c>
       <c r="Q13" t="n">
-        <v>250</v>
+        <v>7</v>
       </c>
       <c r="R13" t="n">
-        <v>1471</v>
+        <v>53</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,17 +1682,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1854673021</t>
+          <t>12859533</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1854673021</t>
+          <t>https://m.place.naver.com/place/12859533</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1692,40 +1704,48 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>세란피부과의원</t>
+          <t>장피부과의원</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lllllhope@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+          <t>1sanginfl@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>jangskin@lycos.co.kr</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>032-434-2987</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 성말로 10</t>
+          <t>인천광역시 남동구 남동대로 892 2층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.jangskin.kr</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1745,13 +1765,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>13</v>
+        <v>4954</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="R14" t="n">
-        <v>13</v>
+        <v>4997</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,17 +1780,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>36631457</t>
+          <t>11595015</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36631457</t>
+          <t>https://m.place.naver.com/place/11595015</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1782,39 +1802,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>데이뷰의원 인천구월점</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>rhythm8084@naver.com</t>
-        </is>
-      </c>
+          <t>메이퓨어의원 인하대역점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1369-7968</t>
+          <t>032-887-0310</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로489번길 4 맨하탄빌딩 6층</t>
+          <t>인천광역시 미추홀구 용정공원로83번길 59 드림빌딩 401호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.daybeauclinic13.com/</t>
+          <t>https://www.maypureclinic.com/ko/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1835,17 +1851,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3151</v>
+        <v>563</v>
       </c>
       <c r="Q15" t="n">
-        <v>7154</v>
+        <v>10</v>
       </c>
       <c r="R15" t="n">
-        <v>10305</v>
+        <v>573</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,17 +1870,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1456260812</t>
+          <t>1415517113</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1456260812</t>
+          <t>https://m.place.naver.com/place/1415517113</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1876,44 +1892,44 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>더샤인의원 인천부평</t>
+          <t>허니즈의원</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>melanindestroyer@naver.com</t>
+          <t>herneeds_clinic@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1353-5435</t>
+          <t>0507-1404-7701</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 열우물로 66 4층</t>
+          <t>인천광역시 남동구 인하로489번길 10 2층 201호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@heoseongwoodr</t>
+          <t>https://www.herneeds-clinic.co.kr/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1924,7 +1940,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1933,13 +1949,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>296</v>
+        <v>620</v>
       </c>
       <c r="Q16" t="n">
-        <v>73</v>
+        <v>726</v>
       </c>
       <c r="R16" t="n">
-        <v>369</v>
+        <v>1346</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1948,17 +1964,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1633242866</t>
+          <t>1841059287</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633242866</t>
+          <t>https://m.place.naver.com/place/1841059287</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1970,29 +1986,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>리앤리의원</t>
+          <t>메인의원 인천주안점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>inme2022@naver.com</t>
+          <t>dudnf8970@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>032-420-0205</t>
+          <t>0507-1334-8970</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로 869 르네상스빌딩</t>
+          <t>인천광역시 미추홀구 미추홀대로 716 204호, 205호, 206호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dudnf8970</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2002,12 +2018,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2023,17 +2039,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>229</v>
+        <v>1433</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>578</v>
       </c>
       <c r="R17" t="n">
-        <v>230</v>
+        <v>2011</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,17 +2058,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>13551782</t>
+          <t>13106424</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13551782</t>
+          <t>https://m.place.naver.com/place/13106424</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2064,35 +2080,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>세이미휴먼피부과의원</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>블리비의원 인천구월점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ksjk-2@naver.com</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>032-435-3114</t>
+          <t>1670-9056</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로 501 4층</t>
+          <t>인천광역시 남동구 인하로489번길 4 맨하탄빌딩 12층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/saybeautyskin/</t>
+          <t>http://www.velyb.kr/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2108,7 +2128,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2117,13 +2137,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1215</v>
+        <v>3052</v>
       </c>
       <c r="Q18" t="n">
-        <v>54</v>
+        <v>5152</v>
       </c>
       <c r="R18" t="n">
-        <v>1269</v>
+        <v>8204</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,17 +2152,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>36477043</t>
+          <t>1056691133</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36477043</t>
+          <t>https://m.place.naver.com/place/1056691133</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2154,29 +2174,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>김의원</t>
+          <t>데이뷰의원 인천구월점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>drkim3119@naver.com</t>
+          <t>rhythm8084@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>032-772-4346</t>
+          <t>0507-1369-7968</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로 61-1 김의원,필라</t>
+          <t>인천광역시 남동구 인하로489번길 4 맨하탄빌딩 6층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.daybeauclinic13.com/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2202,7 +2222,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2211,13 +2231,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>86</v>
+        <v>3306</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>6829</v>
       </c>
       <c r="R19" t="n">
-        <v>90</v>
+        <v>10135</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,17 +2246,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>13240833</t>
+          <t>1456260812</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240833</t>
+          <t>https://m.place.naver.com/place/1456260812</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2248,29 +2268,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>리버스의원 인천구월 터미널역</t>
+          <t>메트로피부과의원</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>wlskfl9087@naver.com</t>
+          <t>yoonbyun1235@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1544-0890</t>
+          <t>032-441-2324</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로 497-22 고려빌딩</t>
+          <t>인천광역시 남동구 인하로 497-5 9층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://ic.reverseclinic.com/</t>
+          <t>https://blog.naver.com/yoonbyun1235</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2296,22 +2316,22 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>632</v>
+        <v>949</v>
       </c>
       <c r="Q20" t="n">
-        <v>2177</v>
+        <v>778</v>
       </c>
       <c r="R20" t="n">
-        <v>2809</v>
+        <v>1727</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,17 +2340,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>356677056</t>
+          <t>33176587</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/356677056</t>
+          <t>https://m.place.naver.com/place/33176587</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2342,34 +2362,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>맑고고운의원 인하대역</t>
+          <t>맑고고운의원 옥련송도역점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>qorwoghk77@naver.com</t>
+          <t>value_trend_guide@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1533-3878</t>
+          <t>032-832-4051</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 311 비젼프라자 4층</t>
+          <t>인천광역시 연수구 독배로40번길 11 효명프라자 4층 405호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.pureskin0108.co.kr</t>
+          <t>https://www.pureskinsongdo.co.kr/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2379,7 +2399,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2399,13 +2419,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>295</v>
+        <v>948</v>
       </c>
       <c r="Q21" t="n">
-        <v>183</v>
+        <v>50</v>
       </c>
       <c r="R21" t="n">
-        <v>478</v>
+        <v>998</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2414,17 +2434,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1008921510</t>
+          <t>1513557735</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008921510</t>
+          <t>https://m.place.naver.com/place/1513557735</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2436,34 +2456,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>뷰티크의원 인천구월</t>
+          <t>한종배피부과의원</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>txnfgw@naver.com</t>
+          <t>oekfkdo@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1395-3851</t>
+          <t>032-428-1252</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 예술로 126 5층 504호, 505호, 506호</t>
+          <t>인천광역시 미추홀구 경인로 431-1</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://beautyqueclinic3.com/?utm_source=naver&amp;utm_medium=referral&amp;utm_campaign=PL_GW</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2484,22 +2504,22 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1858</v>
+        <v>806</v>
       </c>
       <c r="Q22" t="n">
-        <v>6817</v>
+        <v>9</v>
       </c>
       <c r="R22" t="n">
-        <v>8675</v>
+        <v>815</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2508,17 +2528,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1308418932</t>
+          <t>12969596</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1308418932</t>
+          <t>https://m.place.naver.com/place/12969596</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2530,29 +2550,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>닥터쁘띠의원 인천구월</t>
+          <t>CnB맑고고운본점의원</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nervous7314@naver.com</t>
+          <t>cnb_clinic@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1333-3008</t>
+          <t>032-710-7599</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 예술로 126 링크126빌딩 3층</t>
+          <t>인천광역시 미추홀구 미추홀대로 610 현대메디컬프라자 3층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://guwol.doctorpetit.com/</t>
+          <t>https://www.pureclinic.co.kr/theme/basic/</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2587,13 +2607,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1716</v>
+        <v>2004</v>
       </c>
       <c r="Q23" t="n">
-        <v>4541</v>
+        <v>407</v>
       </c>
       <c r="R23" t="n">
-        <v>6257</v>
+        <v>2411</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,17 +2622,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1657854067</t>
+          <t>1193965591</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657854067</t>
+          <t>https://m.place.naver.com/place/1193965591</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2624,29 +2644,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CnB맑고고운본점의원</t>
+          <t>인천 맘모스헤어라인의원</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>cnb_clinic@naver.com</t>
+          <t>dawoonam@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>032-710-7599</t>
+          <t>0507-1346-5855</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 610 현대메디컬프라자 3층</t>
+          <t>인천광역시 남동구 예술로140번길 35 위너스글로벌타워 3층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.pureclinic.co.kr/theme/basic/</t>
+          <t>https://www.mammothincheon.com</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2681,13 +2701,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1997</v>
+        <v>11</v>
       </c>
       <c r="Q24" t="n">
-        <v>406</v>
+        <v>62</v>
       </c>
       <c r="R24" t="n">
-        <v>2403</v>
+        <v>73</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2696,17 +2716,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1193965591</t>
+          <t>1388271254</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1193965591</t>
+          <t>https://m.place.naver.com/place/1388271254</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2718,29 +2738,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>연세아름필의원</t>
+          <t>맑고고운의원 인하대역</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sejongtheareum@naver.com</t>
+          <t>qorwoghk77@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>032-884-0517</t>
+          <t>1533-3878</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 토금남로 53 2층 202호</t>
+          <t>인천광역시 미추홀구 독배로 311 비젼프라자 4층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.pureskin0108.co.kr</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2750,7 +2770,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2775,13 +2795,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>414</v>
+        <v>299</v>
       </c>
       <c r="Q25" t="n">
-        <v>22</v>
+        <v>187</v>
       </c>
       <c r="R25" t="n">
-        <v>436</v>
+        <v>486</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2790,17 +2810,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>13241344</t>
+          <t>1008921510</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13241344</t>
+          <t>https://m.place.naver.com/place/1008921510</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2812,34 +2832,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>인천CNP차앤박피부과</t>
+          <t>더지움의원</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>cnpskin07@naver.com</t>
+          <t>thejiumclinic@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>032-455-1155</t>
+          <t>1522-5428</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 예술로 138 이토타워 4층</t>
+          <t>인천광역시 남동구 인하로507번길 63 모아메디컬타운 4층 더지움의원</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.cnpskin.com/pc/branch/main/main.html?jijummid=cnpskin13</t>
+          <t>https://blog.naver.com/thejiumclinic</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2849,7 +2869,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2860,22 +2880,22 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1645</v>
+        <v>250</v>
       </c>
       <c r="Q26" t="n">
-        <v>14</v>
+        <v>117</v>
       </c>
       <c r="R26" t="n">
-        <v>1659</v>
+        <v>367</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2884,17 +2904,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>11705835</t>
+          <t>755377407</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11705835</t>
+          <t>https://m.place.naver.com/place/755377407</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2906,29 +2926,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>메디에스의원</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>wngml212@naver.com</t>
-        </is>
-      </c>
+          <t>세란피부과의원</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>032-504-9661</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 경원대로 1238 이화빌딩 3층</t>
+          <t>인천광역시 남동구 성말로 10</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://www.medies.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2938,7 +2950,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2963,13 +2975,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>513</v>
+        <v>13</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>517</v>
+        <v>13</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2978,17 +2990,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>12057291</t>
+          <t>36631457</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12057291</t>
+          <t>https://m.place.naver.com/place/36631457</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3000,34 +3012,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>마이모의원</t>
+          <t>김의원</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mymo_clinic@naver.com</t>
+          <t>drkim3119@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1470-5880</t>
+          <t>032-772-4346</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 예술로 138 이토타워 3층 마이모의원</t>
+          <t>인천광역시 중구 우현로 61-1 김의원,필라</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://mymoclinic.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3037,7 +3049,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3048,22 +3060,22 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>183</v>
+        <v>86</v>
       </c>
       <c r="Q28" t="n">
-        <v>575</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>758</v>
+        <v>90</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3072,17 +3084,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1851938775</t>
+          <t>13240833</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1851938775</t>
+          <t>https://m.place.naver.com/place/13240833</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3094,29 +3106,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>오라클피부과의원 구월점</t>
+          <t>제로의원 인천구월</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>gworacle1@naver.com</t>
+          <t>hyangi@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>032-434-5311</t>
+          <t>032-435-3337</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 예술로 126 링크126 6층</t>
+          <t>인천광역시 남동구 예술로 126 8층 제로클리닉의원</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://kuwolskin.com</t>
+          <t>https://zeroclinic0.com</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3126,12 +3138,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3142,7 +3154,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3151,13 +3163,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1577</v>
+        <v>518</v>
       </c>
       <c r="Q29" t="n">
-        <v>1027</v>
+        <v>3639</v>
       </c>
       <c r="R29" t="n">
-        <v>2604</v>
+        <v>4157</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3166,17 +3178,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>21575952</t>
+          <t>1799343573</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21575952</t>
+          <t>https://m.place.naver.com/place/1799343573</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3188,48 +3200,44 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>장피부과의원</t>
+          <t>연세비뇨기과의원</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1sanginfl@naver.com</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>jangskin@lycos.co.kr</t>
-        </is>
-      </c>
+          <t>urouno1@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>032-434-2987</t>
+          <t>032-766-6363</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 남동대로 892 2층</t>
+          <t>인천광역시 중구 우현로 86 2층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://www.jangskin.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3249,13 +3257,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>4954</v>
+        <v>151</v>
       </c>
       <c r="Q30" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4998</v>
+        <v>151</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3264,17 +3272,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>11595015</t>
+          <t>11715237</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11595015</t>
+          <t>https://m.place.naver.com/place/11715237</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3286,34 +3294,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>이지피부과</t>
+          <t>썸블리의원</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>towhsb@naver.com</t>
+          <t>pparksomin@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>032-437-2012</t>
+          <t>0507-1488-1110</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 남동대로 893</t>
+          <t>인천광역시 남동구 인하로507번길 18 4층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://some3vely.kr</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3323,7 +3331,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3334,22 +3342,22 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>257</v>
+        <v>1032</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1818</v>
       </c>
       <c r="R31" t="n">
-        <v>257</v>
+        <v>2850</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3358,17 +3366,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>13238880</t>
+          <t>1446767766</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13238880</t>
+          <t>https://m.place.naver.com/place/1446767766</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3380,48 +3388,44 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>더마티스트의원 인천</t>
+          <t>주안참고운의원</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>dermartist_clinic@naver.com</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>4leaf.ysh@gmail.com</t>
-        </is>
-      </c>
+          <t>kimo23k@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1301-7985</t>
+          <t>032-862-7582</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 예술로 126 7층 701호</t>
+          <t>인천광역시 미추홀구 제일로 38</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.Dermartist.com/</t>
+          <t>http://chamgowoon.com/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3432,22 +3436,22 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1428</v>
+        <v>169</v>
       </c>
       <c r="Q32" t="n">
-        <v>4821</v>
+        <v>76</v>
       </c>
       <c r="R32" t="n">
-        <v>6249</v>
+        <v>245</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3456,17 +3460,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1541439004</t>
+          <t>21361808</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1541439004</t>
+          <t>https://m.place.naver.com/place/21361808</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3478,29 +3482,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>모식외과의원</t>
+          <t>수피부과의원</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>oveitall@naver.com</t>
+          <t>98sooho2@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1404-7894</t>
+          <t>032-888-3888</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로 497-5 푸른세상안과빌딩 12층 1203호</t>
+          <t>인천광역시 미추홀구 낙섬서로 4 현대메디켈센타 2층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://www.hairdoctor4u.com/</t>
+          <t>https://blog.naver.com/98sooho2</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3515,7 +3519,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3535,13 +3539,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>49</v>
+        <v>488</v>
       </c>
       <c r="Q33" t="n">
-        <v>140</v>
+        <v>8</v>
       </c>
       <c r="R33" t="n">
-        <v>189</v>
+        <v>496</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3550,17 +3554,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>11880566</t>
+          <t>35168885</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11880566</t>
+          <t>https://m.place.naver.com/place/35168885</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3572,34 +3576,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>뉴리즈의원 인천</t>
+          <t>아가파의원 주안점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>newrizzclinic@naver.com</t>
+          <t>agafar@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>032-429-7522</t>
+          <t>032-427-4416</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 성말로 10 효명프라자 4층 뉴리즈의원</t>
+          <t>인천광역시 미추홀구 경원대로 858 2F</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@newrizzclinic</t>
+          <t>http://www.agafarclinic.com/</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3609,7 +3613,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3620,7 +3624,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3629,13 +3633,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>967</v>
+        <v>2037</v>
       </c>
       <c r="Q34" t="n">
-        <v>673</v>
+        <v>31</v>
       </c>
       <c r="R34" t="n">
-        <v>1640</v>
+        <v>2068</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3644,17 +3648,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1157284242</t>
+          <t>1554591616</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1157284242</t>
+          <t>https://m.place.naver.com/place/1554591616</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3666,34 +3670,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>더지움의원</t>
+          <t>리엔장의원 인천</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>thejiumclinic@naver.com</t>
+          <t>8832707@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1522-5428</t>
+          <t>0507-1435-3625</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로507번길 63 모아메디컬타운 4층 더지움의원</t>
+          <t>인천광역시 남동구 인하로489번길 4 7층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thejiumclinic</t>
+          <t>https://intro.lienjang.net/re/Oycmsf</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3703,7 +3707,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3714,7 +3718,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3723,13 +3727,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>248</v>
+        <v>1006</v>
       </c>
       <c r="Q35" t="n">
-        <v>94</v>
+        <v>464</v>
       </c>
       <c r="R35" t="n">
-        <v>342</v>
+        <v>1470</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3738,17 +3742,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>755377407</t>
+          <t>1138694952</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/755377407</t>
+          <t>https://m.place.naver.com/place/1138694952</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3760,44 +3764,44 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>메트로피부과의원</t>
+          <t>VS라인의원 인천구월점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>yoonbyun1235@naver.com</t>
+          <t>vsline_official@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>032-441-2324</t>
+          <t>0507-1436-7591</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로 497-5 9층</t>
+          <t>인천광역시 남동구 인하로507번길 9 하나빌딩 4층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yoonbyun1235</t>
+          <t>http://ingw.vsline.kr</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3808,7 +3812,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3817,13 +3821,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>949</v>
+        <v>3680</v>
       </c>
       <c r="Q36" t="n">
-        <v>772</v>
+        <v>10064</v>
       </c>
       <c r="R36" t="n">
-        <v>1721</v>
+        <v>13744</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3832,17 +3836,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>33176587</t>
+          <t>31059087</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33176587</t>
+          <t>https://m.place.naver.com/place/31059087</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3854,29 +3858,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>사랑해차의원</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>social_forum@naver.com</t>
-        </is>
-      </c>
+          <t>메디에스의원</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>032-422-0046</t>
+          <t>032-504-9661</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 남동대로 900</t>
+          <t>인천광역시 부평구 경원대로 1238 이화빌딩 3층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://www.lovecha.co.kr/</t>
+          <t>http://www.medies.co.kr/</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3911,13 +3911,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>221</v>
+        <v>513</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>222</v>
+        <v>517</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3926,17 +3926,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>12872897</t>
+          <t>12057291</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12872897</t>
+          <t>https://m.place.naver.com/place/12057291</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3948,33 +3948,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>서울수피부과의원</t>
+          <t>리브의원 인천</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>seoulsu7975@naver.com</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>admin@seoulsu.com</t>
-        </is>
-      </c>
+          <t>reev_incheon@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>032-424-7975</t>
+          <t>032-724-8544</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 성말로13번길 15 메인프라자 406호</t>
+          <t>인천광역시 남동구 예술로140번길 35 5층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://seoulsu.com</t>
+          <t>https://incheon.reevclinic.com/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3984,12 +3980,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4000,7 +3996,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4009,13 +4005,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>1160</v>
       </c>
       <c r="R38" t="n">
-        <v>259</v>
+        <v>1463</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4024,17 +4020,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>11860488</t>
+          <t>1113664560</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11860488</t>
+          <t>https://m.place.naver.com/place/1113664560</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4046,34 +4042,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>닥터에버스의원 인천</t>
+          <t>오르S의원</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>daplan1@naver.com</t>
+          <t>wolsey0430@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1439-2082</t>
+          <t>0507-1411-9388</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로507번길 24 태림빌딩 3층</t>
+          <t>인천광역시 남동구 인하로 515 1~2층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://drevers.co.kr</t>
+          <t>http://orps.co.kr/sclinic/m_index.html</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4083,7 +4079,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4103,13 +4099,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>9370</v>
+        <v>513</v>
       </c>
       <c r="Q39" t="n">
-        <v>2396</v>
+        <v>140</v>
       </c>
       <c r="R39" t="n">
-        <v>11766</v>
+        <v>653</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4118,17 +4114,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1323699179</t>
+          <t>13139364</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1323699179</t>
+          <t>https://m.place.naver.com/place/13139364</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4140,29 +4136,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>주안참고운의원</t>
+          <t>하프의원 인천</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>kimo23k@naver.com</t>
+          <t>chjh0421@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>032-862-7582</t>
+          <t>032-428-7212</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 제일로 38</t>
+          <t>인천광역시 남동구 인하로 497-5 4층 401호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://chamgowoon.com/</t>
+          <t>https://halfclinic2.com/</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4172,7 +4168,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4188,22 +4184,22 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>169</v>
+        <v>69</v>
       </c>
       <c r="Q40" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="R40" t="n">
-        <v>245</v>
+        <v>154</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4212,17 +4208,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>21361808</t>
+          <t>2009568151</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21361808</t>
+          <t>https://m.place.naver.com/place/2009568151</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4234,34 +4230,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>오르S의원</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>wolsey0430@naver.com</t>
-        </is>
-      </c>
+          <t>밴스의원 구월</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1411-9388</t>
+          <t>0507-1461-9097</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로 515 1~2층</t>
+          <t>인천광역시 남동구 성말로 9 5층 밴스의원</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://orps.co.kr/sclinic/m_index.html</t>
+          <t>https://guwol.vandsclinic.co.kr/?channel=4796&amp;detailChannel=0&amp;gChannel=0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4287,17 +4279,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>513</v>
+        <v>5357</v>
       </c>
       <c r="Q41" t="n">
-        <v>140</v>
+        <v>4246</v>
       </c>
       <c r="R41" t="n">
-        <v>653</v>
+        <v>9603</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4306,17 +4298,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>13139364</t>
+          <t>1471652039</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13139364</t>
+          <t>https://m.place.naver.com/place/1471652039</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4328,44 +4320,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>맑고고운의원 옥련송도역점</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>value_trend_guide@naver.com</t>
-        </is>
-      </c>
+          <t>연세아름필의원</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>032-832-4051</t>
+          <t>032-884-0517</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 독배로40번길 11 효명프라자 4층 405호</t>
+          <t>인천광역시 미추홀구 토금남로 53 2층 202호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.pureskinsongdo.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4385,13 +4373,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>948</v>
+        <v>414</v>
       </c>
       <c r="Q42" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="R42" t="n">
-        <v>998</v>
+        <v>436</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4400,17 +4388,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1513557735</t>
+          <t>13241344</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1513557735</t>
+          <t>https://m.place.naver.com/place/13241344</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4422,29 +4410,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>수피부과의원</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>98sooho2@naver.com</t>
-        </is>
-      </c>
+          <t>리버스의원 인천구월 터미널역</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>032-888-3888</t>
+          <t>1544-0890</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬서로 4 현대메디켈센타 2층</t>
+          <t>인천광역시 남동구 인하로 497-22 고려빌딩</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/98sooho2</t>
+          <t>http://ic.reverseclinic.com/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4454,7 +4438,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4470,22 +4454,22 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>488</v>
+        <v>644</v>
       </c>
       <c r="Q43" t="n">
-        <v>8</v>
+        <v>1863</v>
       </c>
       <c r="R43" t="n">
-        <v>496</v>
+        <v>2507</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4494,17 +4478,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>35168885</t>
+          <t>356677056</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35168885</t>
+          <t>https://m.place.naver.com/place/356677056</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4516,44 +4500,44 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>나인문의원</t>
+          <t>오라클피부과의원 구월점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ninemoonclinic@naver.com</t>
+          <t>gworacle1@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1644-8349</t>
+          <t>032-434-5311</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로 501 슈페리어빌딩 6층</t>
+          <t>인천광역시 남동구 예술로 126 링크126 6층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://ninemoonclinic.co.kr</t>
+          <t>http://kuwolskin.com</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4564,7 +4548,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4573,13 +4557,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1336</v>
+        <v>1583</v>
       </c>
       <c r="Q44" t="n">
-        <v>1015</v>
+        <v>1063</v>
       </c>
       <c r="R44" t="n">
-        <v>2351</v>
+        <v>2646</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4588,17 +4572,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1279049941</t>
+          <t>21575952</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1279049941</t>
+          <t>https://m.place.naver.com/place/21575952</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4610,29 +4594,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>아인병원 피부뷰티</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>ainbeauty5800@naver.com</t>
-        </is>
-      </c>
+          <t>모식외과의원</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>032-459-5800</t>
+          <t>0507-1404-7894</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 3층 아인병원 피부뷰티</t>
+          <t>인천광역시 남동구 인하로 497-5 푸른세상안과빌딩 12층 1203호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://www.ainbeauty.co.kr/</t>
+          <t>http://www.hairdoctor4u.com/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4647,7 +4627,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4658,22 +4638,22 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Q45" t="n">
-        <v>307</v>
+        <v>140</v>
       </c>
       <c r="R45" t="n">
-        <v>350</v>
+        <v>190</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4682,17 +4662,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1599688862</t>
+          <t>11880566</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1599688862</t>
+          <t>https://m.place.naver.com/place/11880566</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4704,29 +4684,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>서울피부과의원 홈플러스간석점</t>
+          <t>문피부과의원</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>120voice@naver.com</t>
+          <t>de_calcomani@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>032-874-0983</t>
+          <t>032-867-0365</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 경원대로 971 홈플러스간석점 2F</t>
+          <t>인천광역시 미추홀구 인하로 275</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>http://www.seoulskindt.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4736,7 +4716,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4761,13 +4741,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>715</v>
+        <v>764</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R46" t="n">
-        <v>719</v>
+        <v>770</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4776,17 +4756,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>13400220</t>
+          <t>34414120</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13400220</t>
+          <t>https://m.place.naver.com/place/34414120</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4798,34 +4778,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>삼성수의원</t>
+          <t>케이톡스의원 인천구월</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>lindsay0626@naver.com</t>
+          <t>kafclift1@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1493-8277</t>
+          <t>0507-1381-7831</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 135 6층</t>
+          <t>인천광역시 남동구 인하로507번길 4 한성빌딩 3층 케이톡스의원 인천구월</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://gw.k-tox.com</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4835,7 +4815,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4846,22 +4826,22 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>194</v>
+        <v>1544</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>4250</v>
       </c>
       <c r="R47" t="n">
-        <v>195</v>
+        <v>5794</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4870,17 +4850,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>19513486</t>
+          <t>1264434600</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19513486</t>
+          <t>https://m.place.naver.com/place/1264434600</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4892,29 +4872,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>한종배피부과의원</t>
+          <t>서울피부과의원 홈플러스간석점</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>oekfkdo@naver.com</t>
+          <t>120voice@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>032-428-1252</t>
+          <t>032-874-0983</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 431-1</t>
+          <t>인천광역시 남동구 경원대로 971 홈플러스간석점 2F</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.seoulskindt.co.kr/</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4924,7 +4904,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4949,13 +4929,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>806</v>
+        <v>713</v>
       </c>
       <c r="Q48" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>815</v>
+        <v>717</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4964,17 +4944,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>12969596</t>
+          <t>13400220</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12969596</t>
+          <t>https://m.place.naver.com/place/13400220</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4986,29 +4966,33 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>메이퓨어의원 인하대역점</t>
+          <t>서울수피부과의원</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ahhk23@naver.com</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>seoulsu7975@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>admin@seoulsu.com</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>032-887-0310</t>
+          <t>032-424-7975</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 용정공원로83번길 59 드림빌딩 401호</t>
+          <t>인천광역시 남동구 성말로13번길 15 메인프라자 406호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.maypureclinic.com/ko/</t>
+          <t>https://seoulsu.com</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5018,12 +5002,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5034,22 +5018,22 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>516</v>
+        <v>258</v>
       </c>
       <c r="Q49" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>526</v>
+        <v>259</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5058,17 +5042,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1415517113</t>
+          <t>11860488</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1415517113</t>
+          <t>https://m.place.naver.com/place/11860488</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5080,29 +5064,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>리엔장의원 인천</t>
+          <t>더샤인의원 인천부평</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>8832707@naver.com</t>
+          <t>melanindestroyer@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1435-3625</t>
+          <t>0507-1353-5435</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로489번길 4 7층</t>
+          <t>인천광역시 부평구 열우물로 66 4층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://intro.lienjang.net/re/Oycmsf</t>
+          <t>https://www.youtube.com/@heoseongwoodr</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5128,7 +5112,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5137,13 +5121,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1005</v>
+        <v>296</v>
       </c>
       <c r="Q50" t="n">
-        <v>464</v>
+        <v>75</v>
       </c>
       <c r="R50" t="n">
-        <v>1469</v>
+        <v>371</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5152,17 +5136,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1138694952</t>
+          <t>1633242866</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138694952</t>
+          <t>https://m.place.naver.com/place/1633242866</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5174,33 +5158,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>에이치봄의원</t>
+          <t>리엘르의원 인천점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>sky001iii@naver.com</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>COPYRIGHT2020@HBOM.COM</t>
-        </is>
-      </c>
+          <t>re-ele@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1348-8201</t>
+          <t>1644-2638</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 309 노블레스타워 503, 504호</t>
+          <t>인천광역시 남동구 인하로507번길 63 6층 601호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://www.hbom.kr</t>
+          <t>http://ic.re-ele.com/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5235,13 +5215,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>466</v>
+        <v>2240</v>
       </c>
       <c r="Q51" t="n">
-        <v>166</v>
+        <v>677</v>
       </c>
       <c r="R51" t="n">
-        <v>632</v>
+        <v>2917</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5250,17 +5230,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1722351848</t>
+          <t>1990116476</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722351848</t>
+          <t>https://m.place.naver.com/place/1990116476</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5272,29 +5252,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>제로의원 인천구월</t>
+          <t>닥터에버스의원 인천</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>hyangi@naver.com</t>
+          <t>daplan1@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>032-435-3337</t>
+          <t>0507-1439-2082</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 예술로 126 8층 제로클리닉의원</t>
+          <t>인천광역시 남동구 인하로507번길 24 태림빌딩 3층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://zeroclinic0.com</t>
+          <t>http://drevers.co.kr</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5304,12 +5284,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5320,7 +5300,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5329,13 +5309,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>510</v>
+        <v>9457</v>
       </c>
       <c r="Q52" t="n">
-        <v>3635</v>
+        <v>2829</v>
       </c>
       <c r="R52" t="n">
-        <v>4145</v>
+        <v>12286</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5344,17 +5324,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1799343573</t>
+          <t>1323699179</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1799343573</t>
+          <t>https://m.place.naver.com/place/1323699179</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5366,44 +5346,44 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>아비쥬의원 인천구월</t>
+          <t>아이윌의원 인천</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>wwchs2012@naver.com</t>
+          <t>hee9_2@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1544-0377</t>
+          <t>032-423-4275</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로507번길 4 한성빌딩 9, 10층</t>
+          <t>인천광역시 남동구 성말로13번길 15 메인프라자 3층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wwchs2012</t>
+          <t>http://www.iwillclinic.com/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5414,22 +5394,22 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2550</v>
+        <v>653</v>
       </c>
       <c r="Q53" t="n">
-        <v>111</v>
+        <v>550</v>
       </c>
       <c r="R53" t="n">
-        <v>2661</v>
+        <v>1203</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5438,17 +5418,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>21235475</t>
+          <t>13454957</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21235475</t>
+          <t>https://m.place.naver.com/place/13454957</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5460,39 +5440,35 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>밴스의원 구월</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>hahahaam@naver.com</t>
-        </is>
-      </c>
+          <t>세이미휴먼피부과의원</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1461-9097</t>
+          <t>032-435-3114</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 성말로 9 5층 밴스의원</t>
+          <t>인천광역시 남동구 인하로 501 4층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://guwol.vandsclinic.co.kr/?channel=4796&amp;detailChannel=0&amp;gChannel=0</t>
+          <t>https://www.instagram.com/saybeautyskin/</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5508,22 +5484,22 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>5244</v>
+        <v>1213</v>
       </c>
       <c r="Q54" t="n">
-        <v>3946</v>
+        <v>52</v>
       </c>
       <c r="R54" t="n">
-        <v>9190</v>
+        <v>1265</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5532,17 +5508,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1471652039</t>
+          <t>36477043</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1471652039</t>
+          <t>https://m.place.naver.com/place/36477043</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5554,44 +5530,44 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>아이윌의원 인천</t>
+          <t>아인병원 피부뷰티</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>hee9_2@naver.com</t>
+          <t>ainbeauty5800@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>032-423-4275</t>
+          <t>032-459-5800</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 성말로13번길 15 메인프라자 3층</t>
+          <t>인천광역시 미추홀구 경인로 372 3층 아인병원 피부뷰티</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://www.iwillclinic.com/</t>
+          <t>http://www.ainbeauty.co.kr/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5607,17 +5583,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>653</v>
+        <v>45</v>
       </c>
       <c r="Q55" t="n">
-        <v>550</v>
+        <v>320</v>
       </c>
       <c r="R55" t="n">
-        <v>1203</v>
+        <v>365</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5626,17 +5602,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>13454957</t>
+          <t>1599688862</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13454957</t>
+          <t>https://m.place.naver.com/place/1599688862</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5648,44 +5624,44 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>케이톡스의원 인천구월</t>
+          <t>뉴리즈의원 인천</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>kafclift1@naver.com</t>
+          <t>newrizzclinic@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1381-7831</t>
+          <t>032-429-7522</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로507번길 4 한성빌딩 3층 케이톡스의원 인천구월</t>
+          <t>인천광역시 남동구 성말로 10 효명프라자 4층 뉴리즈의원</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>http://gw.k-tox.com</t>
+          <t>https://www.youtube.com/@newrizzclinic</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5696,7 +5672,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5705,13 +5681,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1516</v>
+        <v>974</v>
       </c>
       <c r="Q56" t="n">
-        <v>5070</v>
+        <v>669</v>
       </c>
       <c r="R56" t="n">
-        <v>6586</v>
+        <v>1643</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5720,17 +5696,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1264434600</t>
+          <t>1157284242</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264434600</t>
+          <t>https://m.place.naver.com/place/1157284242</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5742,24 +5718,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>연세비뇨기과의원</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>urouno1@naver.com</t>
-        </is>
-      </c>
+          <t>이지피부과</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>032-766-6363</t>
+          <t>032-437-2012</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로 86 2층</t>
+          <t>인천광역시 남동구 남동대로 893</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5799,13 +5771,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5814,17 +5786,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>11715237</t>
+          <t>13238880</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11715237</t>
+          <t>https://m.place.naver.com/place/13238880</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5836,44 +5808,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>허니즈의원</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>herneeds_clinic@naver.com</t>
-        </is>
-      </c>
+          <t>사랑해차의원</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1404-7701</t>
+          <t>032-422-0046</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로489번길 10 2층 201호</t>
+          <t>인천광역시 남동구 남동대로 900</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.herneeds-clinic.co.kr/</t>
+          <t>http://www.lovecha.co.kr/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5884,22 +5852,22 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>616</v>
+        <v>221</v>
       </c>
       <c r="Q58" t="n">
-        <v>720</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>1336</v>
+        <v>222</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5908,17 +5876,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1841059287</t>
+          <t>12872897</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1841059287</t>
+          <t>https://m.place.naver.com/place/12872897</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5930,29 +5898,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>아가파의원 주안점</t>
+          <t>뷰티온의원 인하대역점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>agafar@naver.com</t>
+          <t>handshake2022@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>032-427-4416</t>
+          <t>0507-1326-8461</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로 858 2F</t>
+          <t>인천광역시 미추홀구 독배로317번길 15 2층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://www.agafarclinic.com/</t>
+          <t>https://inhadae.beautyon.co.kr/</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5967,7 +5935,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5978,22 +5946,22 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1911</v>
+        <v>27</v>
       </c>
       <c r="Q59" t="n">
-        <v>31</v>
+        <v>125</v>
       </c>
       <c r="R59" t="n">
-        <v>1942</v>
+        <v>152</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6002,66 +5970,66 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1554591616</t>
+          <t>2051994156</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1554591616</t>
+          <t>https://m.place.naver.com/place/2051994156</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>내과</t>
+          <t>피부과</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>한사랑내과의원</t>
+          <t>마이모의원</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jjj2823@naver.com</t>
+          <t>mymo_clinic@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>032-865-1171</t>
+          <t>0507-1470-5880</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 수봉로 22-1 새마을금고 5층</t>
+          <t>인천광역시 남동구 예술로 138 이토타워 3층 마이모의원</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://www.oneluvclinic.com/</t>
+          <t>https://mymoclinic.co.kr</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6072,7 +6040,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6081,13 +6049,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>528</v>
+        <v>186</v>
       </c>
       <c r="Q60" t="n">
-        <v>84</v>
+        <v>586</v>
       </c>
       <c r="R60" t="n">
-        <v>612</v>
+        <v>772</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6096,17 +6064,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>13241140</t>
+          <t>1851938775</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13241140</t>
+          <t>https://m.place.naver.com/place/1851938775</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6168,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6212,29 +6180,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>후생의원</t>
+          <t>한사랑내과의원</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>lovelyminalee@naver.com</t>
+          <t>jjj2823@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>032-522-0077</t>
+          <t>032-865-1171</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 경인로 772</t>
+          <t>인천광역시 미추홀구 수봉로 22-1 새마을금고 5층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.oneluvclinic.com/</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6244,7 +6212,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6265,17 +6233,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="Q62" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="R62" t="n">
-        <v>526</v>
+        <v>613</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6284,46 +6252,46 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>13239509</t>
+          <t>13241140</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13239509</t>
+          <t>https://m.place.naver.com/place/13241140</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>내과</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>봄헤어뷰티살롱</t>
+          <t>후생의원</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>yallycry@naver.com</t>
+          <t>lovelyminalee@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1352-3237</t>
+          <t>032-522-0077</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 문학길 76 골드파크 2동 1층</t>
+          <t>인천광역시 남동구 경인로 772</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6363,13 +6331,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>45</v>
+        <v>522</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R63" t="n">
-        <v>45</v>
+        <v>526</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6378,61 +6346,57 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1518061009</t>
+          <t>13239509</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1518061009</t>
+          <t>https://m.place.naver.com/place/13239509</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>병원,의원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>연세모벨르의원 인천점</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>73pfzk3l@naver.com</t>
-        </is>
-      </c>
+          <t>봄헤어뷰티살롱</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>032-422-2784</t>
+          <t>0507-1352-3237</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인하로507번길 18 망고빌딩 7층</t>
+          <t>인천광역시 미추홀구 문학길 76 골드파크 2동 1층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_VcjwG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6448,22 +6412,22 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>378</v>
+        <v>45</v>
       </c>
       <c r="Q64" t="n">
-        <v>438</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>816</v>
+        <v>45</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6472,17 +6436,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>31487784</t>
+          <t>1518061009</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31487784</t>
+          <t>https://m.place.naver.com/place/1518061009</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6497,11 +6461,7 @@
           <t>피앤비의원</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>pnb_communication@naver.com</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
@@ -6576,7 +6536,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6588,39 +6548,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>현대성모의원</t>
+          <t>연세모벨르의원 인천점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>eungbo14@naver.com</t>
+          <t>73pfzk3l@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>032-816-1367</t>
+          <t>032-422-2784</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 함박뫼로 28</t>
+          <t>인천광역시 남동구 인하로507번길 18 망고빌딩 7층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_VcjwG</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6636,22 +6596,22 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>160</v>
+        <v>385</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>374</v>
       </c>
       <c r="R66" t="n">
-        <v>161</v>
+        <v>759</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6660,46 +6620,42 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>13240955</t>
+          <t>31487784</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240955</t>
+          <t>https://m.place.naver.com/place/31487784</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>비뇨의학과</t>
+          <t>병원,의원</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>한상희비뇨기과의원</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>yurim2224@naver.com</t>
-        </is>
-      </c>
+          <t>현대성모의원</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>032-862-5005</t>
+          <t>032-816-1367</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 347 국제빌딩 4층 한상희비뇨기과</t>
+          <t>인천광역시 연수구 함박뫼로 28</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6739,13 +6695,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>788</v>
+        <v>160</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>789</v>
+        <v>161</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6754,17 +6710,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>13241098</t>
+          <t>13240955</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13241098</t>
+          <t>https://m.place.naver.com/place/13240955</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6776,25 +6732,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>인하비뇨기과의원</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>이인의비뇨기과의원</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>binterest@naver.com</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>032-891-6181</t>
+          <t>032-427-2929</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로 36 2층</t>
+          <t>인천광역시 미추홀구 미추홀대로 574</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://inhadematouro.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6829,13 +6789,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>369</v>
+        <v>67</v>
       </c>
       <c r="Q68" t="n">
         <v>2</v>
       </c>
       <c r="R68" t="n">
-        <v>371</v>
+        <v>69</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6844,17 +6804,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>13241427</t>
+          <t>13238740</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13241427</t>
+          <t>https://m.place.naver.com/place/13238740</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6826,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>이인의비뇨기과의원</t>
+          <t>인하비뇨기과의원</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6877,18 +6837,18 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>032-427-2929</t>
+          <t>032-891-6181</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 574</t>
+          <t>인천광역시 미추홀구 낙섬중로 36 2층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://inhadematouro.co.kr/</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6898,7 +6858,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6923,13 +6883,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>67</v>
+        <v>369</v>
       </c>
       <c r="Q69" t="n">
         <v>2</v>
       </c>
       <c r="R69" t="n">
-        <v>69</v>
+        <v>371</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6938,51 +6898,47 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>13238740</t>
+          <t>13241427</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13238740</t>
+          <t>https://m.place.naver.com/place/13241427</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>산부인과</t>
+          <t>비뇨의학과</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>W여성병원</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>jeilwomen@naver.com</t>
-        </is>
-      </c>
+          <t>한상희비뇨기과의원</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>032-451-0000</t>
+          <t>032-862-5005</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 400 W여성병원</t>
+          <t>인천광역시 미추홀구 경인로 347 국제빌딩 4층 한상희비뇨기과</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>http://www.w여성병원.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6997,7 +6953,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7013,17 +6969,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>6165</v>
+        <v>786</v>
       </c>
       <c r="Q70" t="n">
-        <v>2168</v>
+        <v>2</v>
       </c>
       <c r="R70" t="n">
-        <v>8333</v>
+        <v>788</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7032,17 +6988,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>12322359</t>
+          <t>13241098</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12322359</t>
+          <t>https://m.place.naver.com/place/13241098</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7046,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7115,13 +7071,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>566</v>
+        <v>599</v>
       </c>
       <c r="Q71" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="R71" t="n">
-        <v>929</v>
+        <v>964</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7140,7 +7096,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7230,41 +7186,41 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>정신건강의학과</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>인천우리병원</t>
+          <t>아임아인안과의원</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>cheongdamwrd@naver.com</t>
+          <t>basic11259@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>032-715-5300</t>
+          <t>032-719-8813</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석바위로53번길 8 6층</t>
+          <t>인천광역시 미추홀구 경인로 372 아임아인안과 2F</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://www.인천우리병원.net</t>
+          <t>http://immed.co.kr/</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7290,22 +7246,22 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="Q73" t="n">
-        <v>89</v>
+        <v>420</v>
       </c>
       <c r="R73" t="n">
-        <v>99</v>
+        <v>720</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7314,51 +7270,51 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>31833642</t>
+          <t>2075464768</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31833642</t>
+          <t>https://m.place.naver.com/place/2075464768</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>정형외과</t>
+          <t>정신건강의학과</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>척척본의원</t>
+          <t>인천우리병원</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>chucchucbone@naver.com</t>
+          <t>cheongdamwrd@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1416-8878</t>
+          <t>032-715-5300</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 14 401호, 402호, 403호</t>
+          <t>인천광역시 미추홀구 석바위로53번길 8 6층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://chukchukbone.kr/</t>
+          <t>http://www.인천우리병원.net</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7373,7 +7329,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7389,17 +7345,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>906</v>
+        <v>10</v>
       </c>
       <c r="Q74" t="n">
-        <v>386</v>
+        <v>97</v>
       </c>
       <c r="R74" t="n">
-        <v>1292</v>
+        <v>107</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7408,51 +7364,51 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1272730632</t>
+          <t>31833642</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1272730632</t>
+          <t>https://m.place.naver.com/place/31833642</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>준종합병원</t>
+          <t>정형외과</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>아인병원</t>
+          <t>척척본의원</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ainwh2022@naver.com</t>
+          <t>chucchucbone@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>032-247-2000</t>
+          <t>0507-1416-8878</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 아인병원</t>
+          <t>인천광역시 미추홀구 숙골로87번길 14 401호, 402호, 403호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.ainwh.co.kr/</t>
+          <t>https://chukchukbone.kr/</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7487,13 +7443,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1126</v>
+        <v>919</v>
       </c>
       <c r="Q75" t="n">
-        <v>5327</v>
+        <v>386</v>
       </c>
       <c r="R75" t="n">
-        <v>6453</v>
+        <v>1305</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7502,51 +7458,51 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1113409160</t>
+          <t>1272730632</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1113409160</t>
+          <t>https://m.place.naver.com/place/1272730632</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>한방병원</t>
+          <t>준종합병원</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>경희백한방병원</t>
+          <t>아인병원</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>khbaekhospital@naver.com</t>
+          <t>ainwh2022@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>032-887-1079</t>
+          <t>032-247-2000</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 아암대로 91</t>
+          <t>인천광역시 미추홀구 경인로 372 아인병원</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://khbmc.com/</t>
+          <t>https://www.ainwh.co.kr/</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7577,17 +7533,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>266</v>
+        <v>1137</v>
       </c>
       <c r="Q76" t="n">
-        <v>5652</v>
+        <v>5391</v>
       </c>
       <c r="R76" t="n">
-        <v>5918</v>
+        <v>6528</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7596,17 +7552,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>13241397</t>
+          <t>1113409160</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13241397</t>
+          <t>https://m.place.naver.com/place/1113409160</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
